--- a/www/download/COUNTRY.BEL.rpPE.xlsx
+++ b/www/download/COUNTRY.BEL.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.7299483476926</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.767200650712243</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.885559181066731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.89852905874464</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.938262384526172</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1.08271977599631</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1.1165698681726</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.05752964628676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.884017016719317</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.803923186934283</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.803793926163139</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.796431999331189</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.729660720440948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.679902075880751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.71694868628827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>-0.568016785904564</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>-0.541308197350857</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.904</t>
+          <t>-0.487740902699892</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>-0.483685109768991</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>-0.457279264187362</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>-0.375308436900433</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>-0.393071161071465</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>-0.433376104019217</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>-0.480810875421085</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>-0.527583231959458</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.258</t>
+          <t>-0.517873936346793</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>-0.518120784742687</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>-0.527089021159156</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>-0.530364958000509</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>-0.533928597772941</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>-0.694770149754517</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>-0.683484334650554</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>-0.65238652333989</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>-0.658250609701474</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>-0.639519299602348</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>-0.596546908457939</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.608745219510564</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.639717104220993</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>-0.680551724508375</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.507</t>
+          <t>-0.696141267677207</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>-0.686084975330373</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>-0.683774344072436</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>-0.689845470897404</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>-0.695340646446326</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>-0.703317870814382</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>-0.895420068484899</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>-0.889019280370699</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>-0.878360582364244</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>-0.88522087317355</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>-0.883650088356651</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>-0.871137375968772</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>-0.875451641403158</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>-0.884605403007702</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>-0.903933071066451</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>-0.897388876618857</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>-0.891385192249994</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>-0.887148720464619</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>-0.876471928226245</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>-0.874998237572002</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>-0.879020950536058</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>34258345506.209</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>32332814735.2372</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>30972317048.0592</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>33095987306.6822</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>34828760503.0265</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>39440671070.5347</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>39597836545.9002</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>38295008599.3554</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>37869087187.7886</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>42768134287.9893</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>41029709143.8168</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>43059218129.7648</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>42349604585.523</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>47482581760.2586</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>37119555108.6266</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>50167889314.2036</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>47383684273.4539</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>43923715269.6767</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>47555487280.0519</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>47484973729.6408</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>45063718763.834</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>47480145508.1477</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>50725491719.7482</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>53629246339.1724</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>58480661026.216</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>56218220916.0115</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>55123371413.057</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>53289907078.2163</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>53435975175.8477</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>54133539392.488</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>2464123.1408656</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>2438682.9464964</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>2577704.02877681</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>2704652.34307228</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>2948210.61531722</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>3379853.90121113</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>3377860.15671092</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>3173039.68445041</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>2618090.28726076</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>2554945.7161702</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>2415425.00786841</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>2260980.24598999</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>1915127.45228249</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>1904565.06118265</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>1788227.47205863</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>29530.2677962984</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>29483.47376986</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>29460.6662230263</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>29792.5672473833</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>31198.3165499022</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>32601.7092704141</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>31896.0087001403</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>31961.0544997501</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>33689.1283189779</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>37589.189274344</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>40070.4016354868</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>42139.7670337925</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>47592.7380314504</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>54335.0723977233</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>49589.1991151797</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>113032.846440485</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>107916.763659581</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>101139.589422996</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>102534.061506838</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>109238.741468038</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>120350.45390887</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>116555.64725831</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>115730.744352165</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>132681.789815261</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>155662.577117741</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>161805.500640972</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>180565.041372019</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>209914.894423553</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>267421.338725078</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>192576.070322288</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>54.48</t>
+          <t>-0.733550822127886</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>-0.716714801730766</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>55.05</t>
+          <t>-0.683739629648212</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>55.53</t>
+          <t>-0.684588404659595</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>56.06</t>
+          <t>-0.667063645859151</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>-0.617578750197713</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>57.64</t>
+          <t>-0.624885835917966</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>-0.650560829382938</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>57.63</t>
+          <t>-0.696165922766683</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>-0.697125968566822</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>-0.685127540637877</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>-0.68085499481551</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>-0.68226330268733</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>-0.678794526509332</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>-0.681860072928255</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>62182.6622563998</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>61459.7852163008</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>54898.5796373611</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>57959.8632996363</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>58927.178840252</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>54204.1396966795</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>56140.9223292916</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>59000.2544874741</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>73014.0204700645</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>85672.9263729353</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>90857.4369084485</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>96451.1149533829</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>109746.04455259</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>124144.43780264</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>119286.866911306</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7299483476926</t>
+          <t>15831.2162035555</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200650712243</t>
+          <t>14932.5595163254</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559181066731</t>
+          <t>13732.7183948075</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89852905874464</t>
+          <t>14552.7666743228</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262384526172</t>
+          <t>14291.6226183798</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977599631</t>
+          <t>13226.4344738946</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1165698681726</t>
+          <t>13684.5613108973</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964628676</t>
+          <t>14618.7481054166</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017016719317</t>
+          <t>15447.8577322965</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923186934283</t>
+          <t>16675.1336950276</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926163139</t>
+          <t>15776.5055971637</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999331189</t>
+          <t>15271.9587230899</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720440948</t>
+          <t>14510.8619473061</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902075880751</t>
+          <t>14294.049780918</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868628827</t>
+          <t>14564.2105418533</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>24335402203.9226</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>23975986149.1487</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>22347430367.2199</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>23659299172.6399</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>26425108749.0638</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>27777554938.1638</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>29274988098.0315</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>32708221262.7902</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>35970093570.434</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>40686943544.1457</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>39183136346.9556</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>38329024017.2553</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>36228356190.3076</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>31129534455.7833</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>31643421509.8044</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>21848461379.2659</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>20914128971.8399</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>19543256757.2646</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>20639476100.9298</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>22979937279.9364</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>25299927635.8224</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>25501639119.2339</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>27611220424.2519</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>31898696901.3138</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>35369790784.6184</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>34785439447.4405</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>33991913397.0554</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>31689880934.1391</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>26557918864.3645</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>26465067247.4924</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>2486940824.65666</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>3061857177.30873</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>2804173609.95529</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>3019823071.71015</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>3445171469.12743</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>2477627302.34139</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>3773348978.79759</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>5097000838.53831</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>4071396669.12023</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>5317152759.5273</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>4397696899.51502</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>4337110620.19992</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>4538475256.16857</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>4571615591.41883</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>5178354262.31208</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>4218.21454215306</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>4230.17308324938</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>4343.11460547863</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>4590.11135336482</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>4758.20072932028</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>5058.06960193484</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>5133.27277696659</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>5108.3632134165</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>4693.58559932386</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>5050.46496690022</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>4967.58711751924</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>4873.96934585786</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>4610.63335029715</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>4591.32702797895</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>4633.45687964274</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>5023.95828598427</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>5014.46098474233</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>5148.32721397199</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>5466.94788251734</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>5658.91134228663</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>6029.6135095511</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>6097.08542785127</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>6020.78634948281</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>5510.61391046558</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>5945.56599066906</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>5839.72387617432</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>5753.50641594094</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>5407.17194314</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>5362.69295744583</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>5409.6177514601</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-56.8</t>
+          <t>177513.724249902</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-54.13</t>
+          <t>173479.376536638</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-48.77</t>
+          <t>164690.676764728</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-48.37</t>
+          <t>162774.108847925</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-45.73</t>
+          <t>160458.565785168</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-37.53</t>
+          <t>161850.185048457</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-39.31</t>
+          <t>162421.29888976</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-43.34</t>
+          <t>170547.540206467</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-48.08</t>
+          <t>200681.067021766</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-52.76</t>
+          <t>238705.533185001</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-51.79</t>
+          <t>247065.800135292</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-51.81</t>
+          <t>273343.026589669</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-52.71</t>
+          <t>324688.835284459</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-53.04</t>
+          <t>375094.150818069</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-53.39</t>
+          <t>301037.714775515</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-69.48</t>
+          <t>15945061808.6182</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-68.35</t>
+          <t>15164643012.4673</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-65.24</t>
+          <t>14921352743.6471</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>15364050516.6174</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>15940033465.4332</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-59.65</t>
+          <t>18531660497.5259</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>18228519177.7178</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-63.97</t>
+          <t>17679529024.2108</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-68.06</t>
+          <t>17950917591.7496</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-69.61</t>
+          <t>20761737517.5807</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-68.61</t>
+          <t>20538824165.738</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-68.38</t>
+          <t>21830701255.499</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-68.98</t>
+          <t>21908465171.2009</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-69.53</t>
+          <t>25285039708.499</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-70.33</t>
+          <t>18118775486.6395</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-89.54</t>
+          <t>155354.044170616</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-88.9</t>
+          <t>152499.637195941</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-87.84</t>
+          <t>143810.096571035</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>144436.832500273</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-88.37</t>
+          <t>141951.659026442</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-87.11</t>
+          <t>147219.957489576</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-87.55</t>
+          <t>146747.689357156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-88.46</t>
+          <t>148688.660044613</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-90.39</t>
+          <t>175032.757146186</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-89.74</t>
+          <t>210429.495545863</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-89.14</t>
+          <t>221153.776608734</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-88.71</t>
+          <t>246146.915333527</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-87.65</t>
+          <t>292889.792187384</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-87.5</t>
+          <t>354991.525157902</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-87.9</t>
+          <t>275136.130911899</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19428.551</t>
+          <t>31737733667.0335</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19444.084</t>
+          <t>31330484134.8437</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20099.862</t>
+          <t>30007838509.4925</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21718.861</t>
+          <t>31939596097.0878</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22791.86</t>
+          <t>34780529728.4981</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>24775.423</t>
+          <t>39972743693.8929</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25396.989</t>
+          <t>40317781621.4812</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25040.125</t>
+          <t>40528722221.1883</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22926.534</t>
+          <t>43847561758.7852</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>24963.892</t>
+          <t>50693562656.9579</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>24865.597</t>
+          <t>50722951426.2299</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>24788.954</t>
+          <t>51671080784.565</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>23673.183</t>
+          <t>49800043491.6627</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>23863.412</t>
+          <t>51834008678.1562</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>24005.479</t>
+          <t>43154571357.1277</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13367.193</t>
+          <t>22159.6800792858</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13423.096</t>
+          <t>20979.7393406965</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13891.33</t>
+          <t>20880.5801936927</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14999.552</t>
+          <t>18337.2763476516</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15809.474</t>
+          <t>18506.9067587257</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17233.324</t>
+          <t>14630.227558881</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>17810.475</t>
+          <t>15673.6095326039</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17725.474</t>
+          <t>21858.880161855</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16294.393</t>
+          <t>25648.3098755797</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17712.274</t>
+          <t>28276.0376391382</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17701.569</t>
+          <t>25912.0235265583</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>17592.349</t>
+          <t>27196.1112561413</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16932.159</t>
+          <t>31799.0430970755</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>17163.928</t>
+          <t>20102.6256601672</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17222.04</t>
+          <t>25901.5838636155</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>34258.346</t>
+          <t>-15792671858.4153</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>32332.815</t>
+          <t>-16165841122.3763</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>30972.317</t>
+          <t>-15086485765.8454</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>33095.987</t>
+          <t>-16575545580.4704</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>34828.761</t>
+          <t>-18840496263.0649</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>39440.671</t>
+          <t>-21441083196.3671</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>39597.837</t>
+          <t>-22089262443.7634</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>38295.009</t>
+          <t>-22849193196.9775</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>37869.087</t>
+          <t>-25896644167.0356</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>42768.134</t>
+          <t>-29931825139.3772</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>41029.709</t>
+          <t>-30184127260.4919</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>43059.218</t>
+          <t>-29840379529.066</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>42349.605</t>
+          <t>-27891578320.4618</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>47482.582</t>
+          <t>-26548968969.6572</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>37119.555</t>
+          <t>-25035795870.4881</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>117847.10491</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>112987.65254</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>102377.91139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103401.21995</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>100904.07742</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>91991.6699</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>90815.81233</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>97443.41446</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>118505.86321</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>135255.33413</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>137671.1065</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>145710.11847</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>166173.53261</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>183373.46257</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>168451.19134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8950.125</t>
+          <t>0.0252644913529974</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8833.509</t>
+          <t>0.0220593624470564</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>9021.839</t>
+          <t>0.0239556813852598</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9616.457</t>
+          <t>0.0227886677505537</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9947.009</t>
+          <t>0.0175323313582896</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10684.075</t>
+          <t>0.0195937006024185</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10836.137</t>
+          <t>0.0133053958446252</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>10575.832</t>
+          <t>0.0156247310148504</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>9615.31</t>
+          <t>0.0171332513347472</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10327.591</t>
+          <t>0.0199367728433169</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10160.822</t>
+          <t>0.0199199713540407</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10049.041</t>
+          <t>0.0199328828946529</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>9601.67</t>
+          <t>0.020869943253171</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>9647.583</t>
+          <t>0.0148154969255332</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>9558.451</t>
+          <t>0.00752873550948811</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>145787.436978897</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>141086.82183962</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>127201.43659137</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>129745.94339465</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>130798.806343329</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>118625.892780869</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>121459.216405026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>133173.760639047</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>162243.029399309</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>183289.402962845</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>189538.754053939</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>200242.206394935</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>229984.011665091</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>260066.435398422</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>249276.082989467</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>50167.889</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>47383.684</t>
+          <t>166925.935825279</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43923.715</t>
+          <t>150238.850509246</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>47555.487</t>
+          <t>152780.082432811</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>47484.974</t>
+          <t>153789.385768597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45063.719</t>
+          <t>139092.734411134</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>47480.146</t>
+          <t>142257.524134406</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>50725.492</t>
+          <t>155622.068038809</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>53629.246</t>
+          <t>189850.98373018</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>58480.661</t>
+          <t>214418.395190387</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>56218.221</t>
+          <t>221372.722061265</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>55123.371</t>
+          <t>233856.294647683</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>53289.907</t>
+          <t>268463.02295684</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>53435.975</t>
+          <t>304290.862609071</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>54133.539</t>
+          <t>291661.720887746</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-73.36</t>
+          <t>856723.160922217</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-71.67</t>
+          <t>843663.633211832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>758561.906929261</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-68.46</t>
+          <t>779376.667471995</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-66.71</t>
+          <t>783058.218019589</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-61.76</t>
+          <t>715560.663943996</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-62.49</t>
+          <t>718025.400210937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-65.06</t>
+          <t>774142.33641661</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>959426.798719664</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-69.71</t>
+          <t>1117434.49111651</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-68.51</t>
+          <t>1178579.94687948</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-68.09</t>
+          <t>1273352.67021226</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-68.23</t>
+          <t>1476781.63982967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-67.88</t>
+          <t>1691948.83062529</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-68.19</t>
+          <t>1618600.58645843</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.464</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.439</t>
+          <t>174972.110251644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>180485.867200163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>183477.087066379</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.948</t>
+          <t>192019.397675357</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>197541.591392764</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.378</t>
+          <t>204298.36309091</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>205733.840799611</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.618</t>
+          <t>203974.716814737</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.555</t>
+          <t>204434.566816834</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>206651.714656127</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.261</t>
+          <t>211469.592023376</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>218010.089434338</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.905</t>
+          <t>225203.004860929</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>222432.517407521</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>145787.436978897</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>148108.679842194</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>153161.249872419</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>156268.66213584</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>164173.134836257</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>169757.696272514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>176199.126719409</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>177163.450461632</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>175487.571196141</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>176234.781917319</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>177815.765467754</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>181904.498785449</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>187670.198415123</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>193154.220820428</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>190343.137159385</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>83827.3371474317</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80070.467084721</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>73070.4469907535</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75720.8192271894</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>72656.0149914032</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>68224.621108866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>65694.5345055935</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>71096.0202611915</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>89452.1209498204</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107950.963989613</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>114334.715688735</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>121832.704612317</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140566.39357316</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>149211.500500929</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>131472.882622254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13367192863.3488</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13423096394.1322</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13891330458.4145</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>14999552110.1915</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>15809474030.0206</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>17233323650.4042</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>17810475092.7822</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>17725473755.6914</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>16294392574.1807</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>17712273565.8871</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>17701569480.7877</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>17592348655.4067</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>16932159075.1315</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>17163927707.7937</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>17222040274.4616</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19428551004.3927</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19444083943.3588</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20099862285.7376</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>21718860935.8538</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>22791859616.7503</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>24775422637.3646</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25396988650.82</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>25040125305.0361</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>22926534452.7461</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>24963891693.2278</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>24865596822.2651</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>24788953625.5495</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>23673182741.6368</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>23863411580.7672</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>24005479279.7661</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8950125108.89151</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8833508926.92818</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9021839023.79133</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>9616457330.98277</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9947008548.53844</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10684075131.4926</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10836136804.0425</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10575831545.5741</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>9615309978.62098</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10327591412.3265</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>10160822208.5599</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>10049040538.8444</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>9601670440.34281</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>9647582836.4123</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>9558451401.92132</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3867180</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3877602</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3904154</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3972758</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4027605</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4108957</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4165431</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4158946</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4160432</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4198741</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4258009</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4308495</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4378108</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4449893.32227832</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4437555.55062773</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3168922</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3173179</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3198472</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3267797</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3322574</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3407095</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3469614</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3469893</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3471630</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3507058</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3563414</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3609450</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3672415</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3738337</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3716888</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165843288808873</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16971428572366</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.172865910570744</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.175109402495878</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.177047456686726</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.178402507200353</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.179995020415257</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.180132552108903</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.166563098005101</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.191720799927915</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.195351821530963</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.198012537488662</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.203713298460781</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.223534403901085</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.225223664202211</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.445526173294926</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.457877195974051</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.467406095339612</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.475852796445434</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.480561974817937</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.49979139344762</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.511218651781974</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.519639347364957</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.502523407533596</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.545194857547996</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.554528964233844</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.561598394579096</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.573414145424168</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.564980568882856</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.569376291647569</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.388630537896201</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.372408518302289</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.359727994089643</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.349037801058688</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.342390568495337</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.321806099352027</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.308786327802769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30022810052614</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.330913494461304</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.263084342524089</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.250119214235193</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.240389067932242</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.222872556115051</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.21148502721606</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20540004415022</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.285223364862848</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.291625399590196</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.297301535145453</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.304888959609711</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.307423361542342</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.310476575252776</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.311696585941848</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.31320548740358</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.309853912530507</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.319620908584757</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.319148448234882</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.318240658220735</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.322439784655136</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.354172629287933</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.357835761656807</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.544839067806272</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.547047365151056</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.55045635763286</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.555332791139806</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.560603380591902</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.570412628151096</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.576390168294394</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.578501547533332</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.57634864357822</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.584362856768334</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.588550630333424</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.591212951593434</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.587619370817737</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.560973091453563</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.560726850996046</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.16993756733088</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.161327235258748</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.152242107221687</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.139778249250483</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.131973257865756</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.119110796596128</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.111913245763758</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.108292965063088</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.113797443891273</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0960162346469096</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0923009214316938</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0905463901858312</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0899408445271269</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0848542792585045</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0814373873471467</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>565662.49026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>551434.48693</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>507003.8431</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>522685.70802</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>523220.59463</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>492505.09565</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>496622.57662</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>526176.36293</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>637060.47889</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>745492.87068</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>783492.97772</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>848835.80683</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>978761.05105</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1103399.79032</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>972907.41524</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>256265.39088</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>246996.40291</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>223309.2975</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>228500.90166</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226445.40076</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>207317.35552</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>207952.05864</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>226718.0883</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>279303.10468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>322369.35918</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>335707.43775</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355688.99926</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>409029.41653</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>453502.36311</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>423134.60351</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>625363.65605692</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>642240.787117299</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>660940.924905751</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>680429.847094052</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>700182.100497513</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>721449.55282383</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>742284.419267126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>759731.713392547</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>776340.031278286</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>796201.566599279</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>818671.25242229</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>841202.487809592</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>866528.736035931</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>892642.539159863</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>914298.655567405</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
